--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_unityProjects\ComputerBasics_DaniTech_Work\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0045878D-1073-4E56-B4AB-E337975A9ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1694337C-9733-4041-9094-670C3A0780D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18330" yWindow="1455" windowWidth="16980" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8775" yWindow="300" windowWidth="29640" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zgynNiv2YVTupuAxVwKvj3LXvSi69gCaqo2XUeu/LZo="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>캐릭터 고유 ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>IconPath</t>
+  </si>
+  <si>
+    <t>Id</t>
   </si>
   <si>
     <t>(name)</t>
@@ -36,61 +37,217 @@
     <t>string</t>
   </si>
   <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>skill_fireball_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_normalSword_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>파이어볼</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>검기 날리기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>불로 된 구체를 만들어 날린다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>적을 벨 수 있는 검기를 날린다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_rest_coffee_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>커피 마시기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>PrefabPath</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_instance_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 베기</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방을 가로로 빠르게 벤다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoolDown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Range</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectilePath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 고유 ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>프리팹경로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>데미지</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨타임</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬종류</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>투사체경로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이콘경로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Instance</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_projectile_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 지대</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지 볼</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지를 모아 전방으로 발사한다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변에 전기 지대를 소환해 적에게 지속적인 피해를 준다</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지속시간</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Area</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rojectile</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 종류</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RangeType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ircle</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ox</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>apsule</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -101,14 +258,21 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -119,14 +283,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,41 +299,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF4D93D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFD86DCD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2F2DB"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FF4D93D9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFD86DCD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFD2F2DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -189,39 +374,238 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF94A5DF"/>
+          <bgColor rgb="FF94A5DF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <border>
+        <left/>
+        <right/>
+        <top style="medium">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF6182D6"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thick">
+          <color rgb="FFFFFFFF"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thick">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD7DFF4"/>
+          <bgColor rgb="FFD7DFF4"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFFFFFFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFFFFFFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFFFFFFF"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFFFFFFF"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFFFFFFF"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
+      <tableStyleElement type="totalRow" dxfId="11"/>
+      <tableStyleElement type="firstColumn" dxfId="10"/>
+      <tableStyleElement type="lastColumn" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -350,21 +734,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -431,388 +815,376 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+  <sheetPr codeName="Sheet1">
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:M996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="51" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
+    <col min="7" max="11" width="12.5703125" style="3"/>
+    <col min="12" max="12" width="15.85546875" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="12.75">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="14"/>
+    </row>
+    <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="11">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="11">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="11">
+        <v>3</v>
+      </c>
+      <c r="G6" s="3">
+        <v>8</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="3">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="J6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <c r="K6" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="5"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="11"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-    </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-    </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1761,12 +2133,9 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1694337C-9733-4041-9094-670C3A0780D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA45F6D-FCC9-48DC-BB73-5ADDE9EC8B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8775" yWindow="300" windowWidth="29640" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>Name</t>
   </si>
@@ -182,60 +182,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>범위 종류</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>RangeType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ircle</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ox</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>apsule</t>
-    </r>
+    <t>Prefabs/Skill/Skill_Instance_Cleave</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -818,21 +765,21 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M996"/>
+  <dimension ref="A1:L996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <col min="3" max="3" width="51" style="3" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="44.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
-    <col min="7" max="11" width="12.5703125" style="3"/>
-    <col min="12" max="12" width="15.85546875" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="12.5703125" style="3"/>
+    <col min="7" max="10" width="12.5703125" style="3"/>
+    <col min="11" max="11" width="15.85546875" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" customHeight="1">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -855,22 +802,19 @@
         <v>22</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="12.75">
+    <row r="2" spans="1:12" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -893,23 +837,20 @@
         <v>8</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="14"/>
-    </row>
-    <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="L2" s="14"/>
+    </row>
+    <row r="3" spans="1:12" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -932,23 +873,20 @@
         <v>13</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1">
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -959,27 +897,26 @@
         <v>11</v>
       </c>
       <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="E4" s="14" t="s">
+        <v>39</v>
+      </c>
       <c r="F4" s="11">
         <v>10</v>
       </c>
       <c r="G4" s="3">
         <v>1.2</v>
       </c>
-      <c r="H4" s="14" t="s">
-        <v>44</v>
+      <c r="H4" s="3">
+        <v>0.3</v>
       </c>
       <c r="I4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="J4" s="3">
         <v>0</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="J4" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -996,20 +933,17 @@
       <c r="G5" s="3">
         <v>3</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>43</v>
+      <c r="H5" s="3">
+        <v>1</v>
       </c>
       <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="J5" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1026,69 +960,66 @@
       <c r="G6" s="3">
         <v>8</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>42</v>
+      <c r="H6" s="3">
+        <v>2</v>
       </c>
       <c r="I6" s="3">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3">
         <v>5</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="J6" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="E7" s="14"/>
       <c r="F7" s="11"/>
     </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="5"/>
       <c r="E8" s="14"/>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA45F6D-FCC9-48DC-BB73-5ADDE9EC8B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDCF82-F337-4B9E-9537-461A8275810D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>Name</t>
   </si>
@@ -183,6 +183,14 @@
   </si>
   <si>
     <t>Prefabs/Skill/Skill_Instance_Cleave</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Skill/Skill_Projectile_EnergyBall</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Skill/Skill_Area_ElectricArea</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -901,7 +909,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="11">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G4" s="3">
         <v>1.2</v>
@@ -926,12 +934,14 @@
       <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="14" t="s">
+        <v>40</v>
+      </c>
       <c r="F5" s="11">
         <v>15</v>
       </c>
       <c r="G5" s="3">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="3">
         <v>1</v>
@@ -953,7 +963,9 @@
       <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="14" t="s">
+        <v>41</v>
+      </c>
       <c r="F6" s="11">
         <v>3</v>
       </c>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDCF82-F337-4B9E-9537-461A8275810D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA1CCC4-6169-4675-A05D-5257E7E9467C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -778,7 +778,7 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="51" style="3" customWidth="1"/>
+    <col min="3" max="3" width="54.85546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="35.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
@@ -909,7 +909,7 @@
         <v>39</v>
       </c>
       <c r="F4" s="11">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G4" s="3">
         <v>1.2</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA1CCC4-6169-4675-A05D-5257E7E9467C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8022D3C9-9588-4DD0-848E-3DB9D7F650E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12075" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9585" yWindow="1125" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -191,6 +191,75 @@
   </si>
   <si>
     <t>Prefabs/Skill/Skill_Area_ElectricArea</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>블레이드</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 주변에 날카로운 블레이드가 회전하며 피해를 입힌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Blade_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rea</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/EnergyBall_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>con/ElectricArea_Icon</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>con/Cleave_Icon</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Skill/Skill_Area_Blade</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -778,8 +847,8 @@
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="61.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="35.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
     <col min="7" max="10" width="12.5703125" style="3"/>
@@ -904,7 +973,9 @@
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="14"/>
+      <c r="D4" s="14" t="s">
+        <v>49</v>
+      </c>
       <c r="E4" s="14" t="s">
         <v>39</v>
       </c>
@@ -934,6 +1005,9 @@
       <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="D5" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="E5" s="14" t="s">
         <v>40</v>
       </c>
@@ -963,6 +1037,9 @@
       <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="E6" s="14" t="s">
         <v>41</v>
       </c>
@@ -973,7 +1050,7 @@
         <v>8</v>
       </c>
       <c r="H6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="3">
         <v>5</v>
@@ -983,11 +1060,36 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="11"/>
+      <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="11">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>3</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8022D3C9-9588-4DD0-848E-3DB9D7F650E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AAF149-3C1E-49FA-AFC9-6945C32E5F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9585" yWindow="1125" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9585" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>전방을 가로로 빠르게 벤다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Damage</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -140,14 +136,6 @@
   </si>
   <si>
     <t>에너지 볼</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>에너지를 모아 전방으로 발사한다</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주변에 전기 지대를 소환해 적에게 지속적인 피해를 준다</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -260,6 +248,18 @@
   </si>
   <si>
     <t>Prefabs/Skill/Skill_Area_Blade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>전방을 가로로 빠르게 벤다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지를 모아 전방으로 발사한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변에 전기 지대를 소환해 적에게 지속적인 피해를 준다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -858,37 +858,37 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="12.75">
@@ -917,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J2" s="14" t="s">
         <v>7</v>
@@ -944,22 +944,22 @@
         <v>6</v>
       </c>
       <c r="F3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="I3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="12" t="s">
+      <c r="K3" s="12" t="s">
         <v>15</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>16</v>
       </c>
       <c r="L3" s="12"/>
     </row>
@@ -971,13 +971,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F4" s="11">
         <v>20</v>
@@ -992,24 +992,24 @@
         <v>0</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F5" s="11">
         <v>15</v>
@@ -1024,24 +1024,24 @@
         <v>0</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F6" s="11">
         <v>3</v>
@@ -1056,24 +1056,24 @@
         <v>5</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>45</v>
-      </c>
       <c r="E7" s="14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F7" s="11">
         <v>10</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AAF149-3C1E-49FA-AFC9-6945C32E5F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F835E6-F877-4E20-A015-72D286E9366C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9585" yWindow="300" windowWidth="23400" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26625" yWindow="855" windowWidth="22275" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>Name</t>
   </si>
@@ -260,6 +260,41 @@
   </si>
   <si>
     <t>주변에 전기 지대를 소환해 적에게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>블랙홀</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 주변에 소환되어 지속적인 피해를 입힌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/BlackHall_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Skill/Skill_Area_BlackHall</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rea</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1092,11 +1127,36 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="11"/>
+      <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="11">
+        <v>25</v>
+      </c>
+      <c r="G8" s="3">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
+        <v>10</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="4"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F835E6-F877-4E20-A015-72D286E9366C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0355FFA-EA66-40B6-9CB3-8429E2989F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26625" yWindow="855" windowWidth="22275" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>Name</t>
   </si>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>ProjectilePath</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>스킬 고유 ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -108,10 +104,6 @@
   </si>
   <si>
     <t>스킬종류</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>투사체경로</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -295,6 +287,114 @@
       </rPr>
       <t>rea</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_instance_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이저</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지를 모아 전방에 레이저를 발사하여 큰 피해를 입힌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Skill/Skill_Instance_Laser</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Laser_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>판정범위</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RangeType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RangeX</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>angeY</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ircle</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ox</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>loat</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>세로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>가로</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -877,7 +977,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L996"/>
+  <dimension ref="A1:M997"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -886,47 +986,53 @@
     <col min="4" max="4" width="25.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="35.42578125" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" style="3" customWidth="1"/>
-    <col min="7" max="10" width="12.5703125" style="3"/>
-    <col min="11" max="11" width="15.85546875" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="12.5703125" style="3"/>
+    <col min="7" max="9" width="12.5703125" style="3"/>
+    <col min="10" max="10" width="15.85546875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="12.5703125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="12.75">
+      <c r="L1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -949,20 +1055,25 @@
         <v>8</v>
       </c>
       <c r="H2" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="L2" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>2</v>
       </c>
@@ -985,20 +1096,25 @@
         <v>12</v>
       </c>
       <c r="H3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="12"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1">
+      <c r="L3" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -1006,194 +1122,241 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F4" s="11">
         <v>20</v>
       </c>
       <c r="G4" s="3">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="I4" s="3">
         <v>0</v>
       </c>
+      <c r="I4" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="J4" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="11">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" s="3">
+        <v>5</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="11">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="11">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>5</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="11">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="11">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="C9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="11">
+        <v>25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3">
+        <v>10</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="3">
         <v>3</v>
       </c>
-      <c r="G6" s="3">
-        <v>8</v>
-      </c>
-      <c r="H6" s="3">
-        <v>3</v>
-      </c>
-      <c r="I6" s="3">
-        <v>5</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="11">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>3</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="11">
-        <v>25</v>
-      </c>
-      <c r="G8" s="3">
-        <v>10</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
-        <v>10</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+    </row>
+    <row r="10" spans="1:13" ht="15.75" customHeight="1">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
+    <row r="14" spans="1:13" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
+    <row r="15" spans="1:13" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1">
+    <row r="16" spans="1:13" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1224,9 +1387,9 @@
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
@@ -1254,9 +1417,9 @@
       <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
@@ -1273,7 +1436,11 @@
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+    </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2238,6 +2405,7 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0355FFA-EA66-40B6-9CB3-8429E2989F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76924DE-5A08-43BC-8F99-C8EB6CF160F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1204,7 +1204,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>15</v>
+        <v>2000</v>
       </c>
       <c r="G6" s="3">
         <v>0.8</v>
@@ -1274,7 +1274,7 @@
         <v>45</v>
       </c>
       <c r="F8" s="11">
-        <v>10</v>
+        <v>100000</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76924DE-5A08-43BC-8F99-C8EB6CF160F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6664BFDE-DAA1-42A8-B95A-43C510483B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1204,7 +1204,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="3">
         <v>0.8</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6664BFDE-DAA1-42A8-B95A-43C510483B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D3A11A-3BB3-40DC-817A-77FA0D901699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="0" windowWidth="31095" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28800" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1204,7 +1204,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="G6" s="3">
         <v>0.8</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D3A11A-3BB3-40DC-817A-77FA0D901699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE6C105-0498-4146-B921-D070736240AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1134,7 +1134,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>65</v>
       </c>
       <c r="K4" s="3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE6C105-0498-4146-B921-D070736240AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B3FA6D-33C3-4697-88C1-7161695A444A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14385" yWindow="315" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -186,10 +186,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Icon/Blade_Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>A</t>
     </r>
@@ -205,40 +201,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Icon/EnergyBall_Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>con/ElectricArea_Icon</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>con/Cleave_Icon</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Prefabs/Skill/Skill_Area_Blade</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -264,10 +226,6 @@
   </si>
   <si>
     <t>플레이어 주변에 소환되어 지속적인 피해를 입힌다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/BlackHall_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -306,10 +264,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Icon/Laser_Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>판정범위</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -395,6 +349,30 @@
   </si>
   <si>
     <t>가로</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon/Cleave_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon//Laser_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon/EnergyBall_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon/ElectricArea_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon/Blade_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon/BlackHall_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1020,16 +998,16 @@
         <v>22</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75">
@@ -1061,16 +1039,16 @@
         <v>7</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
@@ -1102,16 +1080,16 @@
         <v>14</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
@@ -1122,10 +1100,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>34</v>
@@ -1143,7 +1121,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3">
         <v>0.8</v>
@@ -1151,19 +1129,19 @@
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F5" s="11">
         <v>50</v>
@@ -1178,7 +1156,7 @@
         <v>24</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L5" s="3">
         <v>5</v>
@@ -1195,10 +1173,10 @@
         <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>35</v>
@@ -1216,7 +1194,7 @@
         <v>33</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3">
         <v>1</v>
@@ -1230,10 +1208,10 @@
         <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>36</v>
@@ -1251,7 +1229,7 @@
         <v>32</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K7" s="3">
         <v>3</v>
@@ -1268,10 +1246,10 @@
         <v>39</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F8" s="11">
         <v>100000</v>
@@ -1283,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K8" s="3">
         <v>3</v>
@@ -1294,19 +1272,19 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F9" s="11">
         <v>25</v>
@@ -1318,10 +1296,10 @@
         <v>10</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K9" s="3">
         <v>3</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B3FA6D-33C3-4697-88C1-7161695A444A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E72158-91EE-4F56-B270-E1763FB19B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14385" yWindow="315" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -356,10 +356,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Icon/Skill_Icon//Laser_Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon/Skill_Icon/EnergyBall_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -373,6 +369,10 @@
   </si>
   <si>
     <t>Icon/Skill_Icon/BlackHall_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon/Skill_Icon/Laser_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1138,7 +1138,7 @@
         <v>52</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>53</v>
@@ -1176,7 +1176,7 @@
         <v>43</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>35</v>
@@ -1211,7 +1211,7 @@
         <v>44</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>36</v>
@@ -1246,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>41</v>
@@ -1281,7 +1281,7 @@
         <v>47</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>48</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E72158-91EE-4F56-B270-E1763FB19B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BD7031-A21D-4EA6-845C-64C7236A965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1182,7 +1182,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="3">
         <v>0.8</v>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BD7031-A21D-4EA6-845C-64C7236A965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FC15CA-2B26-4BE6-B66A-7439616EB63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3210" yWindow="1335" windowWidth="30030" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>Name</t>
   </si>
@@ -174,15 +174,31 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>skill_area_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>블레이드</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 주변에 날카로운 블레이드가 회전하며 피해를 입힌다.</t>
+    <t>전방을 가로로 빠르게 벤다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>에너지를 모아 전방으로 발사한다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주변에 전기 지대를 소환해 적에게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_area_03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>블랙홀</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 주변에 소환되어 지속적인 피해를 입힌다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Skill/Skill_Area_BlackHall</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -201,53 +217,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Prefabs/Skill/Skill_Area_Blade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>전방을 가로로 빠르게 벤다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>에너지를 모아 전방으로 발사한다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>주변에 전기 지대를 소환해 적에게 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>skill_area_03</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>블랙홀</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 주변에 소환되어 지속적인 피해를 입힌다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefabs/Skill/Skill_Area_BlackHall</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>rea</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>skill_instance_02</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -361,10 +330,6 @@
   </si>
   <si>
     <t>Icon/Skill_Icon/ElectricArea_Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon/Skill_Icon/Blade_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -955,7 +920,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M997"/>
+  <dimension ref="A1:M996"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
@@ -998,16 +963,16 @@
         <v>22</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K1" s="13" t="s">
         <v>21</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75">
@@ -1039,16 +1004,16 @@
         <v>7</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
@@ -1080,16 +1045,16 @@
         <v>14</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
@@ -1100,16 +1065,16 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>34</v>
       </c>
       <c r="F4" s="11">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3">
         <v>0.8</v>
@@ -1121,7 +1086,7 @@
         <v>24</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K4" s="3">
         <v>0.8</v>
@@ -1129,25 +1094,25 @@
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F5" s="11">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="G5" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -1156,7 +1121,7 @@
         <v>24</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L5" s="3">
         <v>5</v>
@@ -1173,16 +1138,16 @@
         <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>10000</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3">
         <v>0.8</v>
@@ -1194,7 +1159,7 @@
         <v>33</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K6" s="3">
         <v>1</v>
@@ -1208,16 +1173,16 @@
         <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>36</v>
       </c>
       <c r="F7" s="11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G7" s="3">
         <v>8</v>
@@ -1229,7 +1194,7 @@
         <v>32</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K7" s="3">
         <v>3</v>
@@ -1237,77 +1202,47 @@
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" s="11">
-        <v>100000</v>
+        <v>40</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H8" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K8" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="11">
-        <v>25</v>
-      </c>
-      <c r="G9" s="3">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3">
-        <v>10</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="3">
-        <v>3</v>
-      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
@@ -1315,9 +1250,9 @@
       <c r="C11" s="1"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
@@ -1365,9 +1300,9 @@
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
       <c r="A23" s="7"/>
@@ -1395,9 +1330,9 @@
       <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
@@ -1414,11 +1349,7 @@
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -2383,7 +2314,6 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FC15CA-2B26-4BE6-B66A-7439616EB63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08F3E5E-0D92-466E-8C86-E8E9521A6475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="1335" windowWidth="30030" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1074,7 +1074,7 @@
         <v>34</v>
       </c>
       <c r="F4" s="11">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3">
         <v>0.8</v>
@@ -1089,7 +1089,7 @@
         <v>54</v>
       </c>
       <c r="K4" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
@@ -1112,7 +1112,7 @@
         <v>120</v>
       </c>
       <c r="G5" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -1147,10 +1147,10 @@
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>54</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
@@ -1182,10 +1182,10 @@
         <v>36</v>
       </c>
       <c r="F7" s="11">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G7" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" s="3">
         <v>5</v>
@@ -1197,7 +1197,7 @@
         <v>54</v>
       </c>
       <c r="K7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
@@ -1217,13 +1217,13 @@
         <v>43</v>
       </c>
       <c r="F8" s="11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G8" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H8" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>44</v>
@@ -1232,7 +1232,7 @@
         <v>54</v>
       </c>
       <c r="K8" s="3">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\06_OZ_Camp\Fork_MyLibrary\Unity_2DMainProject\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08F3E5E-0D92-466E-8C86-E8E9521A6475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC48CC9A-135A-41DA-B47B-F5884DCC1947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="0" windowWidth="30030" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="0" windowWidth="27315" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -1074,7 +1074,7 @@
         <v>34</v>
       </c>
       <c r="F4" s="11">
-        <v>35</v>
+        <v>500</v>
       </c>
       <c r="G4" s="3">
         <v>0.8</v>
@@ -1147,7 +1147,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="11">
-        <v>28</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="3">
         <v>1</v>
